--- a/databases/teste_dunn_clusters_sus_final_kmeans3.xlsx
+++ b/databases/teste_dunn_clusters_sus_final_kmeans3.xlsx
@@ -399,16 +399,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="D2">
-        <v>52.80929579519088</v>
+        <v>53.26961461769033</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.046634071955618</v>
+        <v>-3.043116377936496</v>
       </c>
     </row>
     <row r="3">
@@ -430,16 +430,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D3">
-        <v>56.90685348787246</v>
+        <v>56.45594014193697</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.402072013536458</v>
+        <v>-4.448384826438567</v>
       </c>
     </row>
     <row r="4">
@@ -461,19 +461,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D4">
-        <v>21.03752982612997</v>
+        <v>21.05503349208303</v>
       </c>
       <c r="E4">
-        <v>8.924270720011508E-98</v>
+        <v>6.169140758527798E-98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>-2.614867419965988</v>
+        <v>-2.639196910834099</v>
       </c>
     </row>
   </sheetData>
